--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.67165995174662</v>
+        <v>4.009144742158826</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89212713966916</v>
+        <v>3.882470660196239</v>
       </c>
       <c r="E2" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F2" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.44229443156639</v>
+        <v>2.671872845129539</v>
       </c>
       <c r="D3" t="n">
-        <v>16.13913725199251</v>
+        <v>2.622609803448783</v>
       </c>
       <c r="E3" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F3" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.13037280376832</v>
+        <v>4.571185580612352</v>
       </c>
       <c r="D4" t="n">
-        <v>27.88393969631325</v>
+        <v>4.531140200650903</v>
       </c>
       <c r="E4" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F4" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.31738840567012</v>
+        <v>6.389075615921395</v>
       </c>
       <c r="D5" t="n">
-        <v>38.96734171618591</v>
+        <v>6.332193028880211</v>
       </c>
       <c r="E5" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F5" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.11070453378885</v>
+        <v>3.105489486740689</v>
       </c>
       <c r="D6" t="n">
-        <v>19.60200095697747</v>
+        <v>3.18532515550884</v>
       </c>
       <c r="E6" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F6" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.40213013587205</v>
+        <v>2.990346147079208</v>
       </c>
       <c r="D7" t="n">
-        <v>18.68152940375004</v>
+        <v>3.035748528109382</v>
       </c>
       <c r="E7" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F7" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.86956878635077</v>
+        <v>3.228804927782001</v>
       </c>
       <c r="D8" t="n">
-        <v>19.92620272256744</v>
+        <v>3.238007942417209</v>
       </c>
       <c r="E8" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F8" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.03987184088584</v>
+        <v>3.743979174143949</v>
       </c>
       <c r="D9" t="n">
-        <v>22.63443586220703</v>
+        <v>3.678095827608642</v>
       </c>
       <c r="E9" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F9" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.30451534618317</v>
+        <v>3.949483743754766</v>
       </c>
       <c r="D10" t="n">
-        <v>23.32703354453464</v>
+        <v>3.790642950986879</v>
       </c>
       <c r="E10" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F10" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.7106788597501</v>
+        <v>5.152985314709391</v>
       </c>
       <c r="D11" t="n">
-        <v>32.13310507675313</v>
+        <v>5.221629574972383</v>
       </c>
       <c r="E11" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F11" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.10347936904633</v>
+        <v>6.354315397470029</v>
       </c>
       <c r="D12" t="n">
-        <v>40.3906220648923</v>
+        <v>6.563476085544998</v>
       </c>
       <c r="E12" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F12" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.94168667849688</v>
+        <v>3.728024085255743</v>
       </c>
       <c r="D13" t="n">
-        <v>34.40026520400343</v>
+        <v>5.590043095650558</v>
       </c>
       <c r="E13" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F13" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74444863099664</v>
+        <v>2.395972902536954</v>
       </c>
       <c r="D14" t="n">
-        <v>24.11166268275735</v>
+        <v>3.918145185948069</v>
       </c>
       <c r="E14" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F14" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.52917868573643</v>
+        <v>3.173491536432169</v>
       </c>
       <c r="D15" t="n">
-        <v>18.69033794947519</v>
+        <v>3.037179916789718</v>
       </c>
       <c r="E15" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F15" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>27.77275312135191</v>
+        <v>4.513072382219685</v>
       </c>
       <c r="D16" t="n">
-        <v>27.15948553122808</v>
+        <v>4.413416398824563</v>
       </c>
       <c r="E16" t="n">
-        <v>7.237109003210462</v>
+        <v>1.1760302130217</v>
       </c>
       <c r="F16" t="n">
-        <v>7.287275724403432</v>
+        <v>1.184182305215558</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
